--- a/www/download/IND.surplus_value.empe_ls.r.pc.rpPE.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-75.54</t>
+          <t>-0.755388010499236</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-77.43</t>
+          <t>-0.774277493179727</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-0.775604515427749</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-75.65</t>
+          <t>-0.756498974407135</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.68</t>
+          <t>-0.76682284005554</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.22</t>
+          <t>-0.762174879219015</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-75.05</t>
+          <t>-0.750450442990533</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-76.39</t>
+          <t>-0.763872370595999</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-78.23</t>
+          <t>-0.782259709046344</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>-0.807593235078863</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-80.86</t>
+          <t>-0.808623128935348</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-80.57</t>
+          <t>-0.805651563003364</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-80.43</t>
+          <t>-0.804324656614958</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-78.43</t>
+          <t>-0.784266588776933</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-0.779926028618495</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-83.65</t>
+          <t>-0.836475307270728</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-82.44</t>
+          <t>-0.824391423088032</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-80.35</t>
+          <t>-0.803547710810417</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-81.42</t>
+          <t>-0.814197492310251</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-80.8</t>
+          <t>-0.808043127823695</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.32</t>
+          <t>-0.79323366086325</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-79.35</t>
+          <t>-0.793516443708641</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-0.804371600887363</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-85.56</t>
+          <t>-0.855566668856274</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-0.82818019971856</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-82.05</t>
+          <t>-0.820471399547533</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-81.24</t>
+          <t>-0.812425094722171</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-79.02</t>
+          <t>-0.790215006515937</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-77.67</t>
+          <t>-0.776686395052207</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-78.23</t>
+          <t>-0.782293755665796</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-89.54</t>
+          <t>-0.895420068484899</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>-0.889019280370699</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-87.84</t>
+          <t>-0.878360582364244</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-0.88522087317355</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-88.37</t>
+          <t>-0.883650088356651</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-87.11</t>
+          <t>-0.871137375968772</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-87.55</t>
+          <t>-0.875451641403158</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-88.46</t>
+          <t>-0.884605403007702</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-90.39</t>
+          <t>-0.903933071066451</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-89.74</t>
+          <t>-0.897388876618857</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-89.14</t>
+          <t>-0.891385192249994</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-88.71</t>
+          <t>-0.887148720464619</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-87.65</t>
+          <t>-0.876471928226245</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-87.5</t>
+          <t>-0.874998237572002</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-87.9</t>
+          <t>-0.879020950536058</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>180.49</t>
+          <t>1.80490600619429</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>214.73</t>
+          <t>2.14729878301438</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>282.29</t>
+          <t>2.82285561327608</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>168.49</t>
+          <t>1.6849325630224</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>172.92</t>
+          <t>1.72921140506612</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>178.1</t>
+          <t>1.7810264402042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>149.2</t>
+          <t>1.49201160926853</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>131.05</t>
+          <t>1.31047664802936</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>82.51</t>
+          <t>0.825086517993295</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>0.977572477879688</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>1.00014368873179</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>101.16</t>
+          <t>1.01155418049348</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>85.49</t>
+          <t>0.854883308869056</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>0.727856195170018</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>0.576893702344599</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>149.05</t>
+          <t>1.49054915877565</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>132.25</t>
+          <t>1.32250188357436</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>127.56</t>
+          <t>1.27558547712878</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>119.01</t>
+          <t>1.19014342155774</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>239.54</t>
+          <t>2.39539935961028</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>200.15</t>
+          <t>2.00150135832562</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>241.28</t>
+          <t>2.41277075368553</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>301.64</t>
+          <t>3.01635830039278</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>338.21</t>
+          <t>3.38210730487013</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>293.71</t>
+          <t>2.93711832340842</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>214.25</t>
+          <t>2.14250709278309</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>177.98</t>
+          <t>1.7797554720775</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>165.44</t>
+          <t>1.65440307301749</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>147.91</t>
+          <t>1.47911886556073</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>128.21</t>
+          <t>1.28212742454049</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-72.58</t>
+          <t>-0.725760053440829</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-71.83</t>
+          <t>-0.718250087319701</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-73.78</t>
+          <t>-0.737757657818409</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-0.740026219152922</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-73.96</t>
+          <t>-0.739624302413342</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.09</t>
+          <t>-0.760930734495726</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-76.46</t>
+          <t>-0.764576851117664</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-0.756126866518728</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-75.31</t>
+          <t>-0.753078802225209</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-76.74</t>
+          <t>-0.767362005231725</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-77.59</t>
+          <t>-0.775898045569223</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-78.43</t>
+          <t>-0.784301053550211</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-76.46</t>
+          <t>-0.76461024831783</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-74.52</t>
+          <t>-0.745181320908778</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-74.15</t>
+          <t>-0.741489129025155</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>226.6</t>
+          <t>2.26603669244093</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>193.42</t>
+          <t>1.93421222097359</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>1.73441982959462</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>156.81</t>
+          <t>1.56806934198938</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>163.88</t>
+          <t>1.63875833269607</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>152.04</t>
+          <t>1.5203805990616</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>147.82</t>
+          <t>1.478193604065</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>158.79</t>
+          <t>1.58792143241201</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>185.52</t>
+          <t>1.85522164056084</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>156.12</t>
+          <t>1.56117257946573</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>1.51403753111114</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>140.17</t>
+          <t>1.40170943646948</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>1.33499226037228</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>113.57</t>
+          <t>1.13567219824303</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>0.904370864739915</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-59.43</t>
+          <t>-0.594325943473606</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-59.06</t>
+          <t>-0.590557760528378</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-58.74</t>
+          <t>-0.587368567254177</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-0.62330057573908</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-61.64</t>
+          <t>-0.616417038966138</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-59.1</t>
+          <t>-0.591006231917676</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-60.1</t>
+          <t>-0.600978208955949</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-63.13</t>
+          <t>-0.631280209449725</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-69.65</t>
+          <t>-0.696508817033301</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-68.78</t>
+          <t>-0.687759947129847</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-67.34</t>
+          <t>-0.673407270789351</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-65.75</t>
+          <t>-0.657506527985732</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-62.62</t>
+          <t>-0.62622879896599</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-62.56</t>
+          <t>-0.625594823412838</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-62.71</t>
+          <t>-0.627078469557614</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103.29</t>
+          <t>1.03286210661699</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>0.397850908284304</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>0.457106860452063</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>0.288707676320212</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>0.322343793610313</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>0.302891288172512</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>0.134765977147002</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-0.107170524087196</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-42.97</t>
+          <t>-0.429694514678209</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-0.255939529286266</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-28.07</t>
+          <t>-0.2807154240185</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-0.307693822490952</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-34.59</t>
+          <t>-0.34592125245158</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-42.87</t>
+          <t>-0.428716363400325</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-37.18</t>
+          <t>-0.371768205337191</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-83.41</t>
+          <t>-0.834137815552767</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-82.24</t>
+          <t>-0.822425262022598</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-80.2</t>
+          <t>-0.802039489459421</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-81.33</t>
+          <t>-0.813318690167184</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-80.95</t>
+          <t>-0.809502859516776</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-0.794638623628993</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-80.02</t>
+          <t>-0.800227950253204</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-81</t>
+          <t>-0.810021544083596</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-82.16</t>
+          <t>-0.821578037126475</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-81.95</t>
+          <t>-0.81952457341122</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-81.49</t>
+          <t>-0.814870347978144</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-80.3</t>
+          <t>-0.803028963876584</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-78.99</t>
+          <t>-0.789907791313254</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-77.88</t>
+          <t>-0.778763950248377</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-0.779876439697688</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-86.05</t>
+          <t>-0.860499075698464</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-85.87</t>
+          <t>-0.858686123916193</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-84.75</t>
+          <t>-0.847533355457698</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-85.67</t>
+          <t>-0.85671376407101</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-85.22</t>
+          <t>-0.852203928370429</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-83.92</t>
+          <t>-0.839183844640466</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-84.31</t>
+          <t>-0.843145461152004</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-85.45</t>
+          <t>-0.854456106972329</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-86.01</t>
+          <t>-0.860137323580726</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-87.02</t>
+          <t>-0.870221677538178</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-86.78</t>
+          <t>-0.867808143901884</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-85.85</t>
+          <t>-0.858465354386116</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-0.864372416451923</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-86.09</t>
+          <t>-0.860855813623198</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-86.81</t>
+          <t>-0.868051147874561</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-76.64</t>
+          <t>-0.766420943203382</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-76.37</t>
+          <t>-0.763715972041425</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-73.97</t>
+          <t>-0.73965343246859</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-75.22</t>
+          <t>-0.752161252406543</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-74.18</t>
+          <t>-0.741804393446638</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.76</t>
+          <t>-0.727585195717893</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-73.44</t>
+          <t>-0.73435885771834</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-74.91</t>
+          <t>-0.749066666834311</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-79.15</t>
+          <t>-0.791489807642261</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-78.61</t>
+          <t>-0.786067860450953</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>-0.77791369815215</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-77.41</t>
+          <t>-0.774120467217659</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-0.769665812508285</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-76.98</t>
+          <t>-0.769836191912418</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-77.73</t>
+          <t>-0.77725803558741</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>160.94</t>
+          <t>1.6094293231372</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>115.95</t>
+          <t>1.15949036525004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100.53</t>
+          <t>1.00527206948362</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67.73</t>
+          <t>0.677314073113335</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>0.710052833030689</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>66.29</t>
+          <t>0.662868192987855</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>0.492513405822493</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0.297337703369692</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-0.16481447708367</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-0.06336377757914</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-10.07</t>
+          <t>-0.100729719066691</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-19.38</t>
+          <t>-0.19379361633021</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-0.37811570049697</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-46.55</t>
+          <t>-0.465543035868502</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-48.71</t>
+          <t>-0.487081637407571</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-85.72</t>
+          <t>-0.857237898668129</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-0.84967794970162</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-83.73</t>
+          <t>-0.837293495656111</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-84.44</t>
+          <t>-0.844408450977911</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-83.59</t>
+          <t>-0.835945058497621</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-82.42</t>
+          <t>-0.82422603347103</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-83.33</t>
+          <t>-0.833301440628208</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-83.98</t>
+          <t>-0.83981731450689</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-86.03</t>
+          <t>-0.860349806238941</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-86.13</t>
+          <t>-0.86126422661428</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-85.63</t>
+          <t>-0.856265625985883</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-85.09</t>
+          <t>-0.850864315084803</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-84.52</t>
+          <t>-0.845178352884063</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>-0.84791869465997</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-85.44</t>
+          <t>-0.854436746779072</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-0.854563080311838</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-84.68</t>
+          <t>-0.846841511605418</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-83.63</t>
+          <t>-0.83634621397238</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>-0.847887572620577</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-84.36</t>
+          <t>-0.843594290780453</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-83.55</t>
+          <t>-0.83549116828645</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-83.97</t>
+          <t>-0.839668184621465</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-0.854840108173027</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-88.71</t>
+          <t>-0.887114785149031</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-87.55</t>
+          <t>-0.875513447157127</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-87.1</t>
+          <t>-0.870976197226915</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-86.92</t>
+          <t>-0.869159052918385</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-85.63</t>
+          <t>-0.856315252268178</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-85.3</t>
+          <t>-0.853039654067038</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-85.47</t>
+          <t>-0.854671159801651</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-76.94</t>
+          <t>-0.769437047199975</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-76.75</t>
+          <t>-0.767502216875875</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-78.8</t>
+          <t>-0.788010590529047</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-81.07</t>
+          <t>-0.810681540811137</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-81.44</t>
+          <t>-0.814421578970851</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-82.07</t>
+          <t>-0.8206943257953</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-82.59</t>
+          <t>-0.825908256303059</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-83.69</t>
+          <t>-0.836946416736419</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-83.61</t>
+          <t>-0.836104776469697</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-0.854815394487992</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-0.849703449343948</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-84.66</t>
+          <t>-0.846581432769169</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-84.05</t>
+          <t>-0.840517169337264</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-81.09</t>
+          <t>-0.810893428607848</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-0.795895718860145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-58.53</t>
+          <t>-0.585260888341557</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-58.89</t>
+          <t>-0.588903551578883</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-59.29</t>
+          <t>-0.592939979653452</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-59.72</t>
+          <t>-0.597150670013808</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-59.22</t>
+          <t>-0.592159280430693</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-54.77</t>
+          <t>-0.547670284785724</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-55.12</t>
+          <t>-0.551201659761599</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-61.08</t>
+          <t>-0.610765734609083</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-68.92</t>
+          <t>-0.689163181791611</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-0.683941774777431</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-67.79</t>
+          <t>-0.677901035569189</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-66.88</t>
+          <t>-0.668765545295279</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-65.94</t>
+          <t>-0.659416390977624</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-67.12</t>
+          <t>-0.671239172803603</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-69.72</t>
+          <t>-0.697247278835743</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>0.345950594408446</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>0.397422551057665</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>0.372502228091351</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0.317499969101287</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>0.460456839081741</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.356657348188637</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.166497532176172</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-0.0471168792189127</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-0.443204405191894</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-0.236362826585762</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>-0.240633056280129</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>-0.173261691288194</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-0.205948297048412</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-0.165105572275745</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-0.0586290923130246</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>143.82</t>
+          <t>1.43822382905504</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>116.1</t>
+          <t>1.1610141680128</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>123.83</t>
+          <t>1.23831430348715</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>422.37</t>
+          <t>4.22366850256065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>278.81</t>
+          <t>2.78807123387284</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>257.94</t>
+          <t>2.5793976193008</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>2.83072224209773</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>246.68</t>
+          <t>2.46675753987277</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>225.14</t>
+          <t>2.25136883107592</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>251.48</t>
+          <t>2.51475075211817</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>214.53</t>
+          <t>2.14534248067119</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>138.91</t>
+          <t>1.38908509120045</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>147.94</t>
+          <t>1.47935499460775</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>139.69</t>
+          <t>1.39687869042532</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>117.55</t>
+          <t>1.17549450637944</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1526.36</t>
+          <t>15.2635925208634</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1676.7</t>
+          <t>16.7669745424239</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1431.64</t>
+          <t>14.3163765485035</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1411.37</t>
+          <t>14.1136811745894</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1384.95</t>
+          <t>13.8495191562088</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1383.7</t>
+          <t>13.8369723791934</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1340.02</t>
+          <t>13.4001914544419</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1294.1</t>
+          <t>12.9410006257618</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1341.99</t>
+          <t>13.4199352835383</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1192.72</t>
+          <t>11.9271572521443</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1082.9</t>
+          <t>10.8289735541855</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1029.71</t>
+          <t>10.2971071380366</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>930.5</t>
+          <t>9.30495928368333</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>976.94</t>
+          <t>9.76936242539454</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>879.5</t>
+          <t>8.79503596799979</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-77.96</t>
+          <t>-0.779580105671211</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-77.55</t>
+          <t>-0.775510338305544</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>-0.777916158560055</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-78.31</t>
+          <t>-0.783129840178729</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-0.777717361417888</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.05</t>
+          <t>-0.770536138029914</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-78.26</t>
+          <t>-0.782577325603296</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-79.79</t>
+          <t>-0.797937910401672</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-81.78</t>
+          <t>-0.817806416248623</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-83.67</t>
+          <t>-0.836650809345656</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-0.84040268816968</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-81.97</t>
+          <t>-0.819732156855172</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-0.831362226814102</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-83.98</t>
+          <t>-0.839784866562244</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-84.26</t>
+          <t>-0.842618948478031</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-80.99</t>
+          <t>-0.809864162019997</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-81.77</t>
+          <t>-0.817696482182627</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-80.88</t>
+          <t>-0.808758266465298</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-80.73</t>
+          <t>-0.807314093638259</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-0.798669435452193</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.98</t>
+          <t>-0.779777290076155</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-78.73</t>
+          <t>-0.787343883584775</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-79.8</t>
+          <t>-0.798032706227057</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-83.28</t>
+          <t>-0.832775216008207</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-82.5</t>
+          <t>-0.824961866797554</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-81.7</t>
+          <t>-0.817025743017706</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>-0.807561595308108</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-79.84</t>
+          <t>-0.798413203190005</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-0.802365003835224</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-0.807465929746247</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-86.67</t>
+          <t>-0.866730441398221</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-83.76</t>
+          <t>-0.837589209608557</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-82.96</t>
+          <t>-0.829608921127738</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-82.74</t>
+          <t>-0.827401480043403</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-84.8</t>
+          <t>-0.847979795404924</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-86.36</t>
+          <t>-0.863555305994096</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-84.8</t>
+          <t>-0.847998248873062</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-83.41</t>
+          <t>-0.834111434137592</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-82.28</t>
+          <t>-0.822758723857598</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-82.72</t>
+          <t>-0.827235143893816</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-81.19</t>
+          <t>-0.811873333237655</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-78.44</t>
+          <t>-0.78439727886129</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-74.37</t>
+          <t>-0.743730111456152</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-0.745558090308398</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-78</t>
+          <t>-0.780039936776083</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-48.03</t>
+          <t>-0.48034590595058</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-50.58</t>
+          <t>-0.505755682388635</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-0.467303606539785</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-0.268698364882799</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-39.5</t>
+          <t>-0.394996605224522</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-46.78</t>
+          <t>-0.467784262665056</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-41.22</t>
+          <t>-0.412212719033963</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-45.27</t>
+          <t>-0.452676575234369</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-44.03</t>
+          <t>-0.440319874883036</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-44.35</t>
+          <t>-0.443452762268673</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-51.65</t>
+          <t>-0.516489445183406</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-53.28</t>
+          <t>-0.532789707637982</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-49.77</t>
+          <t>-0.497708063490314</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-37.22</t>
+          <t>-0.372201386688457</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-32.7</t>
+          <t>-0.326960909821327</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>2.58004884694521</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>169.86</t>
+          <t>1.69856248381302</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>109.88</t>
+          <t>1.09884494402973</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>0.811303703723472</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>0.805258516831358</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>84.69</t>
+          <t>0.846861618000531</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>0.610570443063499</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>0.44989159336117</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>0.0406171439090792</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>0.0748046957973199</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>0.0620793380042577</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-0.0390830109514754</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-0.240944191417694</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-0.338800506746391</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-0.283295098492195</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-88.57</t>
+          <t>-0.885722515739907</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-87.83</t>
+          <t>-0.878347120310768</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-86.43</t>
+          <t>-0.864281763643372</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-86.39</t>
+          <t>-0.863916331465774</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-85.11</t>
+          <t>-0.85105998588183</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-83.47</t>
+          <t>-0.834727915681665</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-84.19</t>
+          <t>-0.841860167034207</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-0.852788173113407</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-89.43</t>
+          <t>-0.894333358574009</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-87.19</t>
+          <t>-0.871866513852954</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-86.81</t>
+          <t>-0.868063321308344</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-86.41</t>
+          <t>-0.864080760983451</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-85.62</t>
+          <t>-0.856154900216269</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-86.18</t>
+          <t>-0.861762104756531</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-85.72</t>
+          <t>-0.857194724715113</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>135.76</t>
+          <t>1.35755202756629</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>100.05</t>
+          <t>1.000463563318</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>0.741005558877022</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>0.635468674268124</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>0.596345778919959</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>0.499891097328558</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>0.407862850425196</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>0.351651317171202</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.0146007279726776</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.132509763347462</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-0.0582829845553513</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>-21.1</t>
+          <t>-0.211030273973542</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-35.71</t>
+          <t>-0.357073633675412</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-43.45</t>
+          <t>-0.434517906192547</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-0.303293978283625</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>194.29</t>
+          <t>1.94288091620007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>203.03</t>
+          <t>2.03034610473063</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>150.37</t>
+          <t>1.50366268716772</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>124.46</t>
+          <t>1.24457482934944</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>102.77</t>
+          <t>1.02766341179963</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>0.656451072154316</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>0.507059893207658</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>0.525375984418997</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>0.927381058405414</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>1.03600841471256</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>0.932966576658623</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>105.15</t>
+          <t>1.05147472183293</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>134.25</t>
+          <t>1.34250211092586</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>178.19</t>
+          <t>1.78194691871511</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>217.65</t>
+          <t>2.17647401005982</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-48.87</t>
+          <t>-0.48868507058924</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-0.497468082412896</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-0.498893366217405</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-55.14</t>
+          <t>-0.551382701570597</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-54.3</t>
+          <t>-0.542980620366423</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-53.47</t>
+          <t>-0.534684589450449</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-62.52</t>
+          <t>-0.625243970368378</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-58.32</t>
+          <t>-0.583165450757734</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-66.58</t>
+          <t>-0.66582798583928</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-62.69</t>
+          <t>-0.626867130127967</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-59.79</t>
+          <t>-0.597919703738308</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-59.05</t>
+          <t>-0.590513970855364</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-55.4</t>
+          <t>-0.554019920433488</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-60.88</t>
+          <t>-0.608767791662913</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-60.45</t>
+          <t>-0.604496670308628</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-85.91</t>
+          <t>-0.859094720616243</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-84.88</t>
+          <t>-0.848809274112923</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-83.18</t>
+          <t>-0.831788555600882</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-84.34</t>
+          <t>-0.843355458597436</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-83.78</t>
+          <t>-0.837789958285101</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-83.12</t>
+          <t>-0.831218122695819</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-83.92</t>
+          <t>-0.839204218059248</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-84.74</t>
+          <t>-0.84740424170154</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-88.02</t>
+          <t>-0.880204019524614</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-86.81</t>
+          <t>-0.868062468300536</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-85.94</t>
+          <t>-0.859362546070705</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-0.853419099040364</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-0.84766275263166</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-0.84772674554774</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-0.85231402574177</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>0.123960963537791</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.00651124072196829</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.0152916690364494</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-0.163365181583865</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-0.103016446123548</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-0.0746013612026638</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-0.140823461452246</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-0.125603070428768</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-0.338917988468763</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-0.061980245378896</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-13.34</t>
+          <t>-0.133379634750313</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-0.114145273963571</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-0.0826347284716298</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-22.8</t>
+          <t>-0.228043618961263</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-0.0981516176512545</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-53.39</t>
+          <t>-0.533873062559393</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-54.44</t>
+          <t>-0.544446100868626</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-54.15</t>
+          <t>-0.541519812880807</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-59</t>
+          <t>-0.590026185786896</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-57.97</t>
+          <t>-0.579688837883524</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-56.39</t>
+          <t>-0.563928190090948</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-57.87</t>
+          <t>-0.578735421098969</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-60.31</t>
+          <t>-0.603092353578459</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-68.2</t>
+          <t>-0.682022700139416</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-64.49</t>
+          <t>-0.644913507677004</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-63.14</t>
+          <t>-0.631416714571954</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-0.613204898250128</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-59.85</t>
+          <t>-0.598454781108786</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-59.28</t>
+          <t>-0.592817544359871</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>-0.590178814135316</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>158.07</t>
+          <t>1.58069080989812</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>172.61</t>
+          <t>1.72612841299615</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>197.39</t>
+          <t>1.97391997901347</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>0.90030124548376</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>199.84</t>
+          <t>1.99840088429147</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>138.09</t>
+          <t>1.38087073104782</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>0.972619764276584</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>0.986009150375816</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>0.600194501897827</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>0.667666178641634</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>0.241134991832988</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.162765945455611</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.0232224424826406</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-14.55</t>
+          <t>-0.145474633225152</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>0.0788060509141806</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>311.96</t>
+          <t>3.11960532629767</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>236.64</t>
+          <t>2.36641822557063</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>231.25</t>
+          <t>2.312547774418</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>290.85</t>
+          <t>2.90850134133725</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>554.75</t>
+          <t>5.54750312398172</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>392.07</t>
+          <t>3.92069157618924</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>321.04</t>
+          <t>3.21043886982432</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>257.03</t>
+          <t>2.57030634815664</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>243.59</t>
+          <t>2.43588169021337</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>179.44</t>
+          <t>1.794355231195</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>1.40702994798937</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>103.25</t>
+          <t>1.03245143176387</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>83.92</t>
+          <t>0.839210144855255</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>0.527845870939245</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>90.78</t>
+          <t>0.907845535416994</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>150.72</t>
+          <t>1.50721846593399</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>132.05</t>
+          <t>1.32052464584753</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>109.76</t>
+          <t>1.0975754227049</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>0.853904730083064</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>108.45</t>
+          <t>1.08453678243823</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>105.73</t>
+          <t>1.05727360118661</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>95.61</t>
+          <t>0.956071539961812</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>0.676670089855877</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-0.139741783741935</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>0.221443846950464</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>0.220277053386007</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>16.23</t>
+          <t>0.162316536690926</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.038537058883557</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-0.231309707847996</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-0.319968068397155</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-48.44</t>
+          <t>-0.484426117697684</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-46.84</t>
+          <t>-0.468363457381562</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-45.59</t>
+          <t>-0.455915341451616</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-50.61</t>
+          <t>-0.506055986959519</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-47.62</t>
+          <t>-0.476172000128732</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-45.37</t>
+          <t>-0.45366943461731</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-49.24</t>
+          <t>-0.492438398887279</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-53.15</t>
+          <t>-0.531517259872042</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-55.77</t>
+          <t>-0.557699946053329</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-59.93</t>
+          <t>-0.59926317393815</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>-0.590177991466168</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-58.56</t>
+          <t>-0.585648807406195</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-60.46</t>
+          <t>-0.604616761074922</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-60.3</t>
+          <t>-0.602987521184769</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-59.56</t>
+          <t>-0.595554132434375</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-84.32</t>
+          <t>-0.843164097090497</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-85.64</t>
+          <t>-0.856380859695076</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-84.74</t>
+          <t>-0.847359790597635</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-85.35</t>
+          <t>-0.853548703260675</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-84.58</t>
+          <t>-0.845781415837537</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-0.849662216178172</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-84.4</t>
+          <t>-0.843960014850972</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-85.43</t>
+          <t>-0.854282031493812</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-87.79</t>
+          <t>-0.877878556779564</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-87.9</t>
+          <t>-0.879045121099661</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-87.27</t>
+          <t>-0.872742551166362</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-86.82</t>
+          <t>-0.868201446652414</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-86.75</t>
+          <t>-0.867510114216843</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-85.51</t>
+          <t>-0.855068672016948</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-84.03</t>
+          <t>-0.840345529525891</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>0.700605449157374</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>0.551635437600895</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.31</t>
+          <t>0.34308591696363</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>0.193240609889122</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>0.109069165208885</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>0.0984754701300605</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>0.464113276529239</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>0.520793945930015</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>0.381443349305918</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>0.108225867263858</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.014409428219369</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.0226942418998723</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.0178792010677057</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.00462023948375978</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0.139811833171377</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-57.78</t>
+          <t>-0.577842333337131</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-59.27</t>
+          <t>-0.592696978840344</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-0.59584515563034</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-57.54</t>
+          <t>-0.575391092139889</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-59.34</t>
+          <t>-0.593426730639891</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-62.55</t>
+          <t>-0.625540583321332</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-62.81</t>
+          <t>-0.628073700751162</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-60.43</t>
+          <t>-0.604293891030985</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-54.65</t>
+          <t>-0.546473274623307</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-54.36</t>
+          <t>-0.543569113111036</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-54.57</t>
+          <t>-0.545650941016504</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-51.89</t>
+          <t>-0.518884598922496</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-43.12</t>
+          <t>-0.43116839849369</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-37.9</t>
+          <t>-0.379009323220436</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-0.355209269909907</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-74.83</t>
+          <t>-0.748330629513899</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-74.83</t>
+          <t>-0.748338387923875</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-77.41</t>
+          <t>-0.774109379441243</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-77.91</t>
+          <t>-0.779122408026651</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-78.05</t>
+          <t>-0.780487501914631</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.92</t>
+          <t>-0.799166960475222</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-81.2</t>
+          <t>-0.812004570845422</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-81.16</t>
+          <t>-0.811580031778106</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-79.3</t>
+          <t>-0.792955544856628</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-78.76</t>
+          <t>-0.787648935538067</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-77.6</t>
+          <t>-0.775964905705161</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-76.72</t>
+          <t>-0.767209253904409</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-73.94</t>
+          <t>-0.739430606132006</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-70.76</t>
+          <t>-0.707556750256583</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-73</t>
+          <t>-0.729977553073824</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>156.38</t>
+          <t>1.56381083837253</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>156.92</t>
+          <t>1.56923805143593</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>157.36</t>
+          <t>1.57361084569119</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>161.26</t>
+          <t>1.61256518803672</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>171.34</t>
+          <t>1.71336839867947</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>154.89</t>
+          <t>1.5488558650812</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>162.98</t>
+          <t>1.62977228077854</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>186.64</t>
+          <t>1.86637964889445</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>178.99</t>
+          <t>1.78992794204565</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>194.3</t>
+          <t>1.94295206871298</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>179.72</t>
+          <t>1.79717870115414</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>172.09</t>
+          <t>1.72089104844197</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>175.4</t>
+          <t>1.75400253005955</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>1.52578183074258</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>182.41</t>
+          <t>1.82406430267404</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.251394415438399</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.292222580871519</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309140744546763</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305653634679999</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>0.331329906898271</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324170938074983</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>0.345714899109803</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359874894817778</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348072272129126</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>0.37783672609627</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>0.388366161904179</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392106378694381</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435388875501731</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454961778521963</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0.471318276761859</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
